--- a/hightSchoolClubData.xlsx
+++ b/hightSchoolClubData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1e6b9e99b5651354/code/react/OsakaHightSchool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{F9E79366-B846-41CB-AE17-FD89ED5B434B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B144C358-A69F-40EB-816B-9C8222B0BCD9}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{F9E79366-B846-41CB-AE17-FD89ED5B434B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EA98599-5E0E-4436-953B-71A8F734369F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="60" windowWidth="28800" windowHeight="15420" activeTab="3" xr2:uid="{5914103E-5F7A-41D9-8763-85CA03573C11}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{5914103E-5F7A-41D9-8763-85CA03573C11}"/>
   </bookViews>
   <sheets>
     <sheet name="体育系" sheetId="1" r:id="rId1"/>
@@ -13015,6 +13015,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C20C458-9515-45B1-8A2B-BB3A4053C0E4}">
   <dimension ref="A1:R379"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="35.75" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
